--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funçõa CONCATENAR.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funçõa CONCATENAR.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\pastas\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E04C67-FB73-4408-8605-776FC9874E66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7C13FA-229A-453D-822F-CE2AB47A1E72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -492,8 +492,14 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2" t="str">
+        <f>A3&amp;" "&amp;B3</f>
+        <v>Mariana Silveira</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>_xlfn.CONCAT($A3," ",$B3)</f>
+        <v>Mariana Silveira</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
     </row>
@@ -504,8 +510,14 @@
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2" t="str">
+        <f t="shared" ref="C4:C7" si="0">A4&amp;" "&amp;B4</f>
+        <v>João Souza</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" ref="D4:D7" si="1">_xlfn.CONCAT($A4," ",$B4)</f>
+        <v>João Souza</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
@@ -516,8 +528,14 @@
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Carlos Pereira</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Carlos Pereira</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
@@ -528,8 +546,14 @@
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Humberto Ferreira</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Humberto Ferreira</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
@@ -540,8 +564,14 @@
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Matos</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Maria Matos</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
